--- a/samples/예시데이터_구매현황(26.09).xlsx
+++ b/samples/예시데이터_구매현황(26.09).xlsx
@@ -555,7 +555,7 @@
         <v>999</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N3" t="str">
         <v>EA</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>99900</v>
+        <v>119880</v>
       </c>
       <c r="Q3" t="str">
         <v>본사</v>
@@ -623,7 +623,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>99900</v>
+        <v>119880</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -682,7 +682,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>99900</v>
+        <v>119880</v>
       </c>
       <c r="Q5" t="str">
         <v/>
